--- a/HW4/result/HW4.xlsx
+++ b/HW4/result/HW4.xlsx
@@ -1,122 +1,175 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\T00229\Documents\GitHub\DADS7102\HW4\result\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B59BAE2D-D883-4B50-BC21-6C939F225E60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A823F48C-8B75-48C0-BEE2-64278D99B454}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{34DA60CE-96CD-40DE-89EC-63BE59E8EFBC}"/>
+    <workbookView xWindow="4125" yWindow="2355" windowWidth="21600" windowHeight="11295" activeTab="2" xr2:uid="{34DA60CE-96CD-40DE-89EC-63BE59E8EFBC}"/>
   </bookViews>
   <sheets>
     <sheet name="FixedCost" sheetId="1" r:id="rId1"/>
     <sheet name="CapitalBudget" sheetId="2" r:id="rId2"/>
+    <sheet name="ProdPlanning" sheetId="3" r:id="rId3"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId3"/>
+    <externalReference r:id="rId4"/>
+    <externalReference r:id="rId5"/>
   </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">CapitalBudget!$A$21:$J$149</definedName>
+    <definedName name="AFinish" localSheetId="2">[2]project!$K$6</definedName>
     <definedName name="AFinish">[1]project!$K$6</definedName>
+    <definedName name="BFinish" localSheetId="2">[2]project!$K$7</definedName>
     <definedName name="BFinish">[1]project!$K$7</definedName>
+    <definedName name="CFinish" localSheetId="2">[2]project!$K$8</definedName>
     <definedName name="CFinish">[1]project!$K$8</definedName>
+    <definedName name="DFinish" localSheetId="2">[2]project!$K$9</definedName>
     <definedName name="DFinish">[1]project!$K$9</definedName>
+    <definedName name="EFinish" localSheetId="2">[2]project!$K$10</definedName>
     <definedName name="EFinish">[1]project!$K$10</definedName>
+    <definedName name="FFinish" localSheetId="2">[2]project!$K$11</definedName>
     <definedName name="FFinish">[1]project!$K$11</definedName>
+    <definedName name="GFinish" localSheetId="2">[2]project!$K$12</definedName>
     <definedName name="GFinish">[1]project!$K$12</definedName>
+    <definedName name="HFinish" localSheetId="2">[2]project!$K$13</definedName>
     <definedName name="HFinish">[1]project!$K$13</definedName>
+    <definedName name="IFinish" localSheetId="2">[2]project!$K$14</definedName>
     <definedName name="IFinish">[1]project!$K$14</definedName>
+    <definedName name="invLevels" localSheetId="2">[2]CapitalBudget!$B$10:$H$10</definedName>
     <definedName name="invLevels">[1]CapitalBudget!$B$10:$H$10</definedName>
+    <definedName name="JFinish" localSheetId="2">[2]project!$K$15</definedName>
     <definedName name="JFinish">[1]project!$K$15</definedName>
+    <definedName name="KFinish" localSheetId="2">[2]project!$K$16</definedName>
     <definedName name="KFinish">[1]project!$K$16</definedName>
+    <definedName name="LFinish" localSheetId="2">[2]project!$K$17</definedName>
     <definedName name="LFinish">[1]project!$K$17</definedName>
+    <definedName name="MFinish" localSheetId="2">[2]project!$K$18</definedName>
     <definedName name="MFinish">[1]project!$K$18</definedName>
+    <definedName name="NFinish" localSheetId="2">[2]project!$K$19</definedName>
     <definedName name="NFinish">[1]project!$K$19</definedName>
     <definedName name="solver_adj" localSheetId="1" hidden="1">CapitalBudget!$B$10:$H$10</definedName>
     <definedName name="solver_adj" localSheetId="0" hidden="1">FixedCost!$B$14:$G$15</definedName>
+    <definedName name="solver_adj" localSheetId="2" hidden="1">ProdPlanning!$B$13:$G$13</definedName>
     <definedName name="solver_cvg" localSheetId="1" hidden="1">0.0001</definedName>
     <definedName name="solver_cvg" localSheetId="0" hidden="1">0.0001</definedName>
+    <definedName name="solver_cvg" localSheetId="2" hidden="1">0.0001</definedName>
     <definedName name="solver_drv" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_drv" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_drv" localSheetId="2" hidden="1">1</definedName>
     <definedName name="solver_eng" localSheetId="1" hidden="1">2</definedName>
     <definedName name="solver_eng" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_eng" localSheetId="2" hidden="1">2</definedName>
     <definedName name="solver_est" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_est" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_est" localSheetId="2" hidden="1">1</definedName>
     <definedName name="solver_itr" localSheetId="1" hidden="1">2147483647</definedName>
     <definedName name="solver_itr" localSheetId="0" hidden="1">2147483647</definedName>
+    <definedName name="solver_itr" localSheetId="2" hidden="1">2147483647</definedName>
     <definedName name="solver_lhs1" localSheetId="1" hidden="1">CapitalBudget!$B$14</definedName>
     <definedName name="solver_lhs1" localSheetId="0" hidden="1">FixedCost!$B$14:$G$14</definedName>
+    <definedName name="solver_lhs1" localSheetId="2" hidden="1">ProdPlanning!$B$13:$G$13</definedName>
     <definedName name="solver_lhs2" localSheetId="1" hidden="1">CapitalBudget!$B$10:$H$10</definedName>
     <definedName name="solver_lhs2" localSheetId="0" hidden="1">FixedCost!$B$15:$G$15</definedName>
+    <definedName name="solver_lhs2" localSheetId="2" hidden="1">ProdPlanning!$B$21:$G$21</definedName>
     <definedName name="solver_lhs3" localSheetId="1" hidden="1">CapitalBudget!$C$15</definedName>
     <definedName name="solver_lhs3" localSheetId="0" hidden="1">FixedCost!$B$23:$B$24</definedName>
+    <definedName name="solver_lhs3" localSheetId="2" hidden="1">ProdPlanning!$B$21:$G$21</definedName>
     <definedName name="solver_lhs4" localSheetId="1" hidden="1">CapitalBudget!$B$10:$H$10</definedName>
     <definedName name="solver_lhs4" localSheetId="0" hidden="1">FixedCost!$B$23:$B$24</definedName>
     <definedName name="solver_lhs5" localSheetId="1" hidden="1">CapitalBudget!$B$10:$H$10</definedName>
     <definedName name="solver_mip" localSheetId="1" hidden="1">2147483647</definedName>
     <definedName name="solver_mip" localSheetId="0" hidden="1">2147483647</definedName>
+    <definedName name="solver_mip" localSheetId="2" hidden="1">2147483647</definedName>
     <definedName name="solver_mni" localSheetId="1" hidden="1">30</definedName>
     <definedName name="solver_mni" localSheetId="0" hidden="1">30</definedName>
+    <definedName name="solver_mni" localSheetId="2" hidden="1">30</definedName>
     <definedName name="solver_mrt" localSheetId="1" hidden="1">0.075</definedName>
     <definedName name="solver_mrt" localSheetId="0" hidden="1">0.075</definedName>
+    <definedName name="solver_mrt" localSheetId="2" hidden="1">0.075</definedName>
     <definedName name="solver_msl" localSheetId="1" hidden="1">2</definedName>
     <definedName name="solver_msl" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_msl" localSheetId="2" hidden="1">2</definedName>
     <definedName name="solver_neg" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_neg" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_neg" localSheetId="2" hidden="1">1</definedName>
     <definedName name="solver_nod" localSheetId="1" hidden="1">2147483647</definedName>
     <definedName name="solver_nod" localSheetId="0" hidden="1">2147483647</definedName>
+    <definedName name="solver_nod" localSheetId="2" hidden="1">2147483647</definedName>
     <definedName name="solver_num" localSheetId="1" hidden="1">2</definedName>
     <definedName name="solver_num" localSheetId="0" hidden="1">3</definedName>
+    <definedName name="solver_num" localSheetId="2" hidden="1">3</definedName>
     <definedName name="solver_nwt" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_nwt" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_nwt" localSheetId="2" hidden="1">1</definedName>
     <definedName name="solver_opt" localSheetId="1" hidden="1">CapitalBudget!$B$17</definedName>
     <definedName name="solver_opt" localSheetId="0" hidden="1">FixedCost!$B$30</definedName>
+    <definedName name="solver_opt" localSheetId="2" hidden="1">ProdPlanning!$H$29</definedName>
     <definedName name="solver_pre" localSheetId="1" hidden="1">0.000001</definedName>
     <definedName name="solver_pre" localSheetId="0" hidden="1">0.000001</definedName>
+    <definedName name="solver_pre" localSheetId="2" hidden="1">0.000001</definedName>
     <definedName name="solver_rbv" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_rbv" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_rbv" localSheetId="2" hidden="1">1</definedName>
     <definedName name="solver_rel1" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_rel1" localSheetId="0" hidden="1">5</definedName>
+    <definedName name="solver_rel1" localSheetId="2" hidden="1">1</definedName>
     <definedName name="solver_rel2" localSheetId="1" hidden="1">5</definedName>
     <definedName name="solver_rel2" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_rel2" localSheetId="2" hidden="1">1</definedName>
     <definedName name="solver_rel3" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_rel3" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_rel3" localSheetId="2" hidden="1">3</definedName>
     <definedName name="solver_rel4" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_rel4" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_rel5" localSheetId="1" hidden="1">5</definedName>
     <definedName name="solver_rhs1" localSheetId="1" hidden="1">CapitalBudget!$D$14</definedName>
     <definedName name="solver_rhs1" localSheetId="0" hidden="1">"binary"</definedName>
+    <definedName name="solver_rhs1" localSheetId="2" hidden="1">ProdPlanning!$B$15:$G$15</definedName>
     <definedName name="solver_rhs2" localSheetId="1" hidden="1">"binary"</definedName>
     <definedName name="solver_rhs2" localSheetId="0" hidden="1">FixedCost!$B$17:$G$17</definedName>
+    <definedName name="solver_rhs2" localSheetId="2" hidden="1">ProdPlanning!$B$23:$G$23</definedName>
     <definedName name="solver_rhs3" localSheetId="1" hidden="1">0</definedName>
     <definedName name="solver_rhs3" localSheetId="0" hidden="1">FixedCost!$D$23:$D$24</definedName>
+    <definedName name="solver_rhs3" localSheetId="2" hidden="1">0</definedName>
     <definedName name="solver_rhs4" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_rhs4" localSheetId="0" hidden="1">FixedCost!$D$23:$D$24</definedName>
     <definedName name="solver_rhs5" localSheetId="1" hidden="1">binary</definedName>
     <definedName name="solver_rlx" localSheetId="1" hidden="1">2</definedName>
     <definedName name="solver_rlx" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_rlx" localSheetId="2" hidden="1">2</definedName>
     <definedName name="solver_rsd" localSheetId="1" hidden="1">0</definedName>
     <definedName name="solver_rsd" localSheetId="0" hidden="1">0</definedName>
+    <definedName name="solver_rsd" localSheetId="2" hidden="1">0</definedName>
     <definedName name="solver_scl" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_scl" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_scl" localSheetId="2" hidden="1">1</definedName>
     <definedName name="solver_sho" localSheetId="1" hidden="1">2</definedName>
     <definedName name="solver_sho" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_sho" localSheetId="2" hidden="1">2</definedName>
     <definedName name="solver_ssz" localSheetId="1" hidden="1">100</definedName>
     <definedName name="solver_ssz" localSheetId="0" hidden="1">100</definedName>
+    <definedName name="solver_ssz" localSheetId="2" hidden="1">100</definedName>
     <definedName name="solver_tim" localSheetId="1" hidden="1">2147483647</definedName>
     <definedName name="solver_tim" localSheetId="0" hidden="1">2147483647</definedName>
+    <definedName name="solver_tim" localSheetId="2" hidden="1">2147483647</definedName>
     <definedName name="solver_tol" localSheetId="1" hidden="1">0.01</definedName>
     <definedName name="solver_tol" localSheetId="0" hidden="1">0.01</definedName>
+    <definedName name="solver_tol" localSheetId="2" hidden="1">0.01</definedName>
     <definedName name="solver_typ" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_typ" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_typ" localSheetId="2" hidden="1">2</definedName>
     <definedName name="solver_val" localSheetId="1" hidden="1">0</definedName>
     <definedName name="solver_val" localSheetId="0" hidden="1">0</definedName>
+    <definedName name="solver_val" localSheetId="2" hidden="1">0</definedName>
     <definedName name="solver_ver" localSheetId="1" hidden="1">3</definedName>
     <definedName name="solver_ver" localSheetId="0" hidden="1">3</definedName>
+    <definedName name="solver_ver" localSheetId="2" hidden="1">3</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -131,6 +184,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -171,7 +227,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -193,7 +249,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="68">
   <si>
     <t>Great Threads fixed cost clothing model</t>
   </si>
@@ -332,17 +388,89 @@
   <si>
     <t>total NPV</t>
   </si>
+  <si>
+    <t>Multiperiod production model</t>
+  </si>
+  <si>
+    <t>Input data</t>
+  </si>
+  <si>
+    <t>Initial inventory</t>
+  </si>
+  <si>
+    <t>Holding cost as % of prod cost</t>
+  </si>
+  <si>
+    <t>Month</t>
+  </si>
+  <si>
+    <t>Production cost/unit</t>
+  </si>
+  <si>
+    <t>Holding cost/unit</t>
+  </si>
+  <si>
+    <t>Production plan (all quantities are in 100s of footballs)</t>
+  </si>
+  <si>
+    <t>Production capacity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">produce capacity </t>
+  </si>
+  <si>
+    <t>On hand after production</t>
+  </si>
+  <si>
+    <t>Demand</t>
+  </si>
+  <si>
+    <t>Ending inventory</t>
+  </si>
+  <si>
+    <t>&gt;= 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">for shortage condition </t>
+  </si>
+  <si>
+    <t>Storage capacity</t>
+  </si>
+  <si>
+    <t>inventory condition</t>
+  </si>
+  <si>
+    <t>Summary of costs (all costs are in hundreds of dollars)</t>
+  </si>
+  <si>
+    <t>Totals</t>
+  </si>
+  <si>
+    <t>Holding cost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Production cost </t>
+  </si>
+  <si>
+    <t>fixed setup cost</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="5">
+  <numFmts count="11">
     <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
+    <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0;\-&quot;$&quot;#,##0"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.0;\-&quot;$&quot;#,##0.0"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0.00;\-&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="168" formatCode="0.0000"/>
+    <numFmt numFmtId="169" formatCode="0.000"/>
+    <numFmt numFmtId="170" formatCode="&quot;$&quot;#,##0.000_);\(&quot;$&quot;#,##0.000\)"/>
+    <numFmt numFmtId="174" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="10" x14ac:knownFonts="1">
     <font>
@@ -412,7 +540,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -440,6 +568,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -483,7 +617,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="4">
+  <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
@@ -491,8 +625,10 @@
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="8" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -551,8 +687,27 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="4" fillId="2" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="8" fontId="4" fillId="2" borderId="0" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" xfId="4" applyFont="1"/>
+    <xf numFmtId="43" fontId="4" fillId="6" borderId="2" xfId="4" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="174" fontId="4" fillId="2" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="4">
+  <cellStyles count="6">
+    <cellStyle name="Comma" xfId="4" builtinId="3"/>
+    <cellStyle name="Currency 2" xfId="5" xr:uid="{908E50C9-1B4A-4EAE-92C8-D968DCA7E87C}"/>
     <cellStyle name="Hyperlink" xfId="3" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="2" xr:uid="{695232CE-3EFA-4DCE-8763-2B9D29797D48}"/>
@@ -572,11 +727,8 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Sensitivity Report 1"/>
       <sheetName val="ProductMix"/>
@@ -743,6 +895,180 @@
       <sheetData sheetId="31"/>
       <sheetData sheetId="32"/>
       <sheetData sheetId="33"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="Sensitivity Report 1"/>
+      <sheetName val="ProductMix"/>
+      <sheetName val="ProductMix_add_on"/>
+      <sheetName val="ProductMix2 Sensitivity"/>
+      <sheetName val="ProductMix2"/>
+      <sheetName val="LM_2"/>
+      <sheetName val="Dual"/>
+      <sheetName val="ProdPlanning"/>
+      <sheetName val="project"/>
+      <sheetName val="BlendingOil"/>
+      <sheetName val="Transport1"/>
+      <sheetName val="AssignmentProblem"/>
+      <sheetName val="BinPacking"/>
+      <sheetName val="cuttingStock"/>
+      <sheetName val="MCNF"/>
+      <sheetName val="RedBrandLogistics"/>
+      <sheetName val="HW3"/>
+      <sheetName val="set_covering_model"/>
+      <sheetName val="ShortestPath"/>
+      <sheetName val="Aggregate1"/>
+      <sheetName val="CapitalBudget"/>
+      <sheetName val="FixedCost"/>
+      <sheetName val="Hub"/>
+      <sheetName val="WorkerScheduling"/>
+      <sheetName val="Transport1-2"/>
+      <sheetName val="MMULT"/>
+      <sheetName val="MDETERM"/>
+      <sheetName val="Peakload"/>
+      <sheetName val="Portfolio"/>
+      <sheetName val="EOQ"/>
+      <sheetName val="SVM1"/>
+      <sheetName val="MLE"/>
+      <sheetName val="OLS"/>
+      <sheetName val="Location"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8">
+        <row r="6">
+          <cell r="K6">
+            <v>2</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="K7">
+            <v>6</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="K8">
+            <v>16</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="K9">
+            <v>22</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="K10">
+            <v>20</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="K11">
+            <v>23</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="K12">
+            <v>29</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="K13">
+            <v>38</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="K14">
+            <v>23</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="K15">
+            <v>29</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="K16">
+            <v>34</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="K17">
+            <v>34</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="K18">
+            <v>40</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="K19">
+            <v>40</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="9" refreshError="1"/>
+      <sheetData sheetId="10" refreshError="1"/>
+      <sheetData sheetId="11" refreshError="1"/>
+      <sheetData sheetId="12" refreshError="1"/>
+      <sheetData sheetId="13" refreshError="1"/>
+      <sheetData sheetId="14" refreshError="1"/>
+      <sheetData sheetId="15" refreshError="1"/>
+      <sheetData sheetId="16" refreshError="1"/>
+      <sheetData sheetId="17" refreshError="1"/>
+      <sheetData sheetId="18" refreshError="1"/>
+      <sheetData sheetId="19" refreshError="1"/>
+      <sheetData sheetId="20">
+        <row r="10">
+          <cell r="B10">
+            <v>0</v>
+          </cell>
+          <cell r="C10">
+            <v>1</v>
+          </cell>
+          <cell r="D10">
+            <v>1</v>
+          </cell>
+          <cell r="E10">
+            <v>1</v>
+          </cell>
+          <cell r="F10">
+            <v>0</v>
+          </cell>
+          <cell r="G10">
+            <v>0</v>
+          </cell>
+          <cell r="H10">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="21" refreshError="1"/>
+      <sheetData sheetId="22" refreshError="1"/>
+      <sheetData sheetId="23" refreshError="1"/>
+      <sheetData sheetId="24" refreshError="1"/>
+      <sheetData sheetId="25" refreshError="1"/>
+      <sheetData sheetId="26" refreshError="1"/>
+      <sheetData sheetId="27" refreshError="1"/>
+      <sheetData sheetId="28" refreshError="1"/>
+      <sheetData sheetId="29" refreshError="1"/>
+      <sheetData sheetId="30" refreshError="1"/>
+      <sheetData sheetId="31" refreshError="1"/>
+      <sheetData sheetId="32" refreshError="1"/>
+      <sheetData sheetId="33" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -7447,4 +7773,922 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87743ED0-3CDD-4FFA-AF50-C4DAE5D2AEAC}">
+  <dimension ref="A1:I29"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="28.5703125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="13.140625" style="2" customWidth="1"/>
+    <col min="3" max="7" width="9.140625" style="2"/>
+    <col min="8" max="8" width="12.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="243" width="9.140625" style="2"/>
+    <col min="244" max="244" width="26.5703125" style="2" customWidth="1"/>
+    <col min="245" max="245" width="13.140625" style="2" customWidth="1"/>
+    <col min="246" max="250" width="9.140625" style="2"/>
+    <col min="251" max="251" width="10.85546875" style="2" customWidth="1"/>
+    <col min="252" max="252" width="23" style="2" bestFit="1" customWidth="1"/>
+    <col min="253" max="253" width="10.5703125" style="2" customWidth="1"/>
+    <col min="254" max="254" width="10.85546875" style="2" customWidth="1"/>
+    <col min="255" max="499" width="9.140625" style="2"/>
+    <col min="500" max="500" width="26.5703125" style="2" customWidth="1"/>
+    <col min="501" max="501" width="13.140625" style="2" customWidth="1"/>
+    <col min="502" max="506" width="9.140625" style="2"/>
+    <col min="507" max="507" width="10.85546875" style="2" customWidth="1"/>
+    <col min="508" max="508" width="23" style="2" bestFit="1" customWidth="1"/>
+    <col min="509" max="509" width="10.5703125" style="2" customWidth="1"/>
+    <col min="510" max="510" width="10.85546875" style="2" customWidth="1"/>
+    <col min="511" max="755" width="9.140625" style="2"/>
+    <col min="756" max="756" width="26.5703125" style="2" customWidth="1"/>
+    <col min="757" max="757" width="13.140625" style="2" customWidth="1"/>
+    <col min="758" max="762" width="9.140625" style="2"/>
+    <col min="763" max="763" width="10.85546875" style="2" customWidth="1"/>
+    <col min="764" max="764" width="23" style="2" bestFit="1" customWidth="1"/>
+    <col min="765" max="765" width="10.5703125" style="2" customWidth="1"/>
+    <col min="766" max="766" width="10.85546875" style="2" customWidth="1"/>
+    <col min="767" max="1011" width="9.140625" style="2"/>
+    <col min="1012" max="1012" width="26.5703125" style="2" customWidth="1"/>
+    <col min="1013" max="1013" width="13.140625" style="2" customWidth="1"/>
+    <col min="1014" max="1018" width="9.140625" style="2"/>
+    <col min="1019" max="1019" width="10.85546875" style="2" customWidth="1"/>
+    <col min="1020" max="1020" width="23" style="2" bestFit="1" customWidth="1"/>
+    <col min="1021" max="1021" width="10.5703125" style="2" customWidth="1"/>
+    <col min="1022" max="1022" width="10.85546875" style="2" customWidth="1"/>
+    <col min="1023" max="1267" width="9.140625" style="2"/>
+    <col min="1268" max="1268" width="26.5703125" style="2" customWidth="1"/>
+    <col min="1269" max="1269" width="13.140625" style="2" customWidth="1"/>
+    <col min="1270" max="1274" width="9.140625" style="2"/>
+    <col min="1275" max="1275" width="10.85546875" style="2" customWidth="1"/>
+    <col min="1276" max="1276" width="23" style="2" bestFit="1" customWidth="1"/>
+    <col min="1277" max="1277" width="10.5703125" style="2" customWidth="1"/>
+    <col min="1278" max="1278" width="10.85546875" style="2" customWidth="1"/>
+    <col min="1279" max="1523" width="9.140625" style="2"/>
+    <col min="1524" max="1524" width="26.5703125" style="2" customWidth="1"/>
+    <col min="1525" max="1525" width="13.140625" style="2" customWidth="1"/>
+    <col min="1526" max="1530" width="9.140625" style="2"/>
+    <col min="1531" max="1531" width="10.85546875" style="2" customWidth="1"/>
+    <col min="1532" max="1532" width="23" style="2" bestFit="1" customWidth="1"/>
+    <col min="1533" max="1533" width="10.5703125" style="2" customWidth="1"/>
+    <col min="1534" max="1534" width="10.85546875" style="2" customWidth="1"/>
+    <col min="1535" max="1779" width="9.140625" style="2"/>
+    <col min="1780" max="1780" width="26.5703125" style="2" customWidth="1"/>
+    <col min="1781" max="1781" width="13.140625" style="2" customWidth="1"/>
+    <col min="1782" max="1786" width="9.140625" style="2"/>
+    <col min="1787" max="1787" width="10.85546875" style="2" customWidth="1"/>
+    <col min="1788" max="1788" width="23" style="2" bestFit="1" customWidth="1"/>
+    <col min="1789" max="1789" width="10.5703125" style="2" customWidth="1"/>
+    <col min="1790" max="1790" width="10.85546875" style="2" customWidth="1"/>
+    <col min="1791" max="2035" width="9.140625" style="2"/>
+    <col min="2036" max="2036" width="26.5703125" style="2" customWidth="1"/>
+    <col min="2037" max="2037" width="13.140625" style="2" customWidth="1"/>
+    <col min="2038" max="2042" width="9.140625" style="2"/>
+    <col min="2043" max="2043" width="10.85546875" style="2" customWidth="1"/>
+    <col min="2044" max="2044" width="23" style="2" bestFit="1" customWidth="1"/>
+    <col min="2045" max="2045" width="10.5703125" style="2" customWidth="1"/>
+    <col min="2046" max="2046" width="10.85546875" style="2" customWidth="1"/>
+    <col min="2047" max="2291" width="9.140625" style="2"/>
+    <col min="2292" max="2292" width="26.5703125" style="2" customWidth="1"/>
+    <col min="2293" max="2293" width="13.140625" style="2" customWidth="1"/>
+    <col min="2294" max="2298" width="9.140625" style="2"/>
+    <col min="2299" max="2299" width="10.85546875" style="2" customWidth="1"/>
+    <col min="2300" max="2300" width="23" style="2" bestFit="1" customWidth="1"/>
+    <col min="2301" max="2301" width="10.5703125" style="2" customWidth="1"/>
+    <col min="2302" max="2302" width="10.85546875" style="2" customWidth="1"/>
+    <col min="2303" max="2547" width="9.140625" style="2"/>
+    <col min="2548" max="2548" width="26.5703125" style="2" customWidth="1"/>
+    <col min="2549" max="2549" width="13.140625" style="2" customWidth="1"/>
+    <col min="2550" max="2554" width="9.140625" style="2"/>
+    <col min="2555" max="2555" width="10.85546875" style="2" customWidth="1"/>
+    <col min="2556" max="2556" width="23" style="2" bestFit="1" customWidth="1"/>
+    <col min="2557" max="2557" width="10.5703125" style="2" customWidth="1"/>
+    <col min="2558" max="2558" width="10.85546875" style="2" customWidth="1"/>
+    <col min="2559" max="2803" width="9.140625" style="2"/>
+    <col min="2804" max="2804" width="26.5703125" style="2" customWidth="1"/>
+    <col min="2805" max="2805" width="13.140625" style="2" customWidth="1"/>
+    <col min="2806" max="2810" width="9.140625" style="2"/>
+    <col min="2811" max="2811" width="10.85546875" style="2" customWidth="1"/>
+    <col min="2812" max="2812" width="23" style="2" bestFit="1" customWidth="1"/>
+    <col min="2813" max="2813" width="10.5703125" style="2" customWidth="1"/>
+    <col min="2814" max="2814" width="10.85546875" style="2" customWidth="1"/>
+    <col min="2815" max="3059" width="9.140625" style="2"/>
+    <col min="3060" max="3060" width="26.5703125" style="2" customWidth="1"/>
+    <col min="3061" max="3061" width="13.140625" style="2" customWidth="1"/>
+    <col min="3062" max="3066" width="9.140625" style="2"/>
+    <col min="3067" max="3067" width="10.85546875" style="2" customWidth="1"/>
+    <col min="3068" max="3068" width="23" style="2" bestFit="1" customWidth="1"/>
+    <col min="3069" max="3069" width="10.5703125" style="2" customWidth="1"/>
+    <col min="3070" max="3070" width="10.85546875" style="2" customWidth="1"/>
+    <col min="3071" max="3315" width="9.140625" style="2"/>
+    <col min="3316" max="3316" width="26.5703125" style="2" customWidth="1"/>
+    <col min="3317" max="3317" width="13.140625" style="2" customWidth="1"/>
+    <col min="3318" max="3322" width="9.140625" style="2"/>
+    <col min="3323" max="3323" width="10.85546875" style="2" customWidth="1"/>
+    <col min="3324" max="3324" width="23" style="2" bestFit="1" customWidth="1"/>
+    <col min="3325" max="3325" width="10.5703125" style="2" customWidth="1"/>
+    <col min="3326" max="3326" width="10.85546875" style="2" customWidth="1"/>
+    <col min="3327" max="3571" width="9.140625" style="2"/>
+    <col min="3572" max="3572" width="26.5703125" style="2" customWidth="1"/>
+    <col min="3573" max="3573" width="13.140625" style="2" customWidth="1"/>
+    <col min="3574" max="3578" width="9.140625" style="2"/>
+    <col min="3579" max="3579" width="10.85546875" style="2" customWidth="1"/>
+    <col min="3580" max="3580" width="23" style="2" bestFit="1" customWidth="1"/>
+    <col min="3581" max="3581" width="10.5703125" style="2" customWidth="1"/>
+    <col min="3582" max="3582" width="10.85546875" style="2" customWidth="1"/>
+    <col min="3583" max="3827" width="9.140625" style="2"/>
+    <col min="3828" max="3828" width="26.5703125" style="2" customWidth="1"/>
+    <col min="3829" max="3829" width="13.140625" style="2" customWidth="1"/>
+    <col min="3830" max="3834" width="9.140625" style="2"/>
+    <col min="3835" max="3835" width="10.85546875" style="2" customWidth="1"/>
+    <col min="3836" max="3836" width="23" style="2" bestFit="1" customWidth="1"/>
+    <col min="3837" max="3837" width="10.5703125" style="2" customWidth="1"/>
+    <col min="3838" max="3838" width="10.85546875" style="2" customWidth="1"/>
+    <col min="3839" max="4083" width="9.140625" style="2"/>
+    <col min="4084" max="4084" width="26.5703125" style="2" customWidth="1"/>
+    <col min="4085" max="4085" width="13.140625" style="2" customWidth="1"/>
+    <col min="4086" max="4090" width="9.140625" style="2"/>
+    <col min="4091" max="4091" width="10.85546875" style="2" customWidth="1"/>
+    <col min="4092" max="4092" width="23" style="2" bestFit="1" customWidth="1"/>
+    <col min="4093" max="4093" width="10.5703125" style="2" customWidth="1"/>
+    <col min="4094" max="4094" width="10.85546875" style="2" customWidth="1"/>
+    <col min="4095" max="4339" width="9.140625" style="2"/>
+    <col min="4340" max="4340" width="26.5703125" style="2" customWidth="1"/>
+    <col min="4341" max="4341" width="13.140625" style="2" customWidth="1"/>
+    <col min="4342" max="4346" width="9.140625" style="2"/>
+    <col min="4347" max="4347" width="10.85546875" style="2" customWidth="1"/>
+    <col min="4348" max="4348" width="23" style="2" bestFit="1" customWidth="1"/>
+    <col min="4349" max="4349" width="10.5703125" style="2" customWidth="1"/>
+    <col min="4350" max="4350" width="10.85546875" style="2" customWidth="1"/>
+    <col min="4351" max="4595" width="9.140625" style="2"/>
+    <col min="4596" max="4596" width="26.5703125" style="2" customWidth="1"/>
+    <col min="4597" max="4597" width="13.140625" style="2" customWidth="1"/>
+    <col min="4598" max="4602" width="9.140625" style="2"/>
+    <col min="4603" max="4603" width="10.85546875" style="2" customWidth="1"/>
+    <col min="4604" max="4604" width="23" style="2" bestFit="1" customWidth="1"/>
+    <col min="4605" max="4605" width="10.5703125" style="2" customWidth="1"/>
+    <col min="4606" max="4606" width="10.85546875" style="2" customWidth="1"/>
+    <col min="4607" max="4851" width="9.140625" style="2"/>
+    <col min="4852" max="4852" width="26.5703125" style="2" customWidth="1"/>
+    <col min="4853" max="4853" width="13.140625" style="2" customWidth="1"/>
+    <col min="4854" max="4858" width="9.140625" style="2"/>
+    <col min="4859" max="4859" width="10.85546875" style="2" customWidth="1"/>
+    <col min="4860" max="4860" width="23" style="2" bestFit="1" customWidth="1"/>
+    <col min="4861" max="4861" width="10.5703125" style="2" customWidth="1"/>
+    <col min="4862" max="4862" width="10.85546875" style="2" customWidth="1"/>
+    <col min="4863" max="5107" width="9.140625" style="2"/>
+    <col min="5108" max="5108" width="26.5703125" style="2" customWidth="1"/>
+    <col min="5109" max="5109" width="13.140625" style="2" customWidth="1"/>
+    <col min="5110" max="5114" width="9.140625" style="2"/>
+    <col min="5115" max="5115" width="10.85546875" style="2" customWidth="1"/>
+    <col min="5116" max="5116" width="23" style="2" bestFit="1" customWidth="1"/>
+    <col min="5117" max="5117" width="10.5703125" style="2" customWidth="1"/>
+    <col min="5118" max="5118" width="10.85546875" style="2" customWidth="1"/>
+    <col min="5119" max="5363" width="9.140625" style="2"/>
+    <col min="5364" max="5364" width="26.5703125" style="2" customWidth="1"/>
+    <col min="5365" max="5365" width="13.140625" style="2" customWidth="1"/>
+    <col min="5366" max="5370" width="9.140625" style="2"/>
+    <col min="5371" max="5371" width="10.85546875" style="2" customWidth="1"/>
+    <col min="5372" max="5372" width="23" style="2" bestFit="1" customWidth="1"/>
+    <col min="5373" max="5373" width="10.5703125" style="2" customWidth="1"/>
+    <col min="5374" max="5374" width="10.85546875" style="2" customWidth="1"/>
+    <col min="5375" max="5619" width="9.140625" style="2"/>
+    <col min="5620" max="5620" width="26.5703125" style="2" customWidth="1"/>
+    <col min="5621" max="5621" width="13.140625" style="2" customWidth="1"/>
+    <col min="5622" max="5626" width="9.140625" style="2"/>
+    <col min="5627" max="5627" width="10.85546875" style="2" customWidth="1"/>
+    <col min="5628" max="5628" width="23" style="2" bestFit="1" customWidth="1"/>
+    <col min="5629" max="5629" width="10.5703125" style="2" customWidth="1"/>
+    <col min="5630" max="5630" width="10.85546875" style="2" customWidth="1"/>
+    <col min="5631" max="5875" width="9.140625" style="2"/>
+    <col min="5876" max="5876" width="26.5703125" style="2" customWidth="1"/>
+    <col min="5877" max="5877" width="13.140625" style="2" customWidth="1"/>
+    <col min="5878" max="5882" width="9.140625" style="2"/>
+    <col min="5883" max="5883" width="10.85546875" style="2" customWidth="1"/>
+    <col min="5884" max="5884" width="23" style="2" bestFit="1" customWidth="1"/>
+    <col min="5885" max="5885" width="10.5703125" style="2" customWidth="1"/>
+    <col min="5886" max="5886" width="10.85546875" style="2" customWidth="1"/>
+    <col min="5887" max="6131" width="9.140625" style="2"/>
+    <col min="6132" max="6132" width="26.5703125" style="2" customWidth="1"/>
+    <col min="6133" max="6133" width="13.140625" style="2" customWidth="1"/>
+    <col min="6134" max="6138" width="9.140625" style="2"/>
+    <col min="6139" max="6139" width="10.85546875" style="2" customWidth="1"/>
+    <col min="6140" max="6140" width="23" style="2" bestFit="1" customWidth="1"/>
+    <col min="6141" max="6141" width="10.5703125" style="2" customWidth="1"/>
+    <col min="6142" max="6142" width="10.85546875" style="2" customWidth="1"/>
+    <col min="6143" max="6387" width="9.140625" style="2"/>
+    <col min="6388" max="6388" width="26.5703125" style="2" customWidth="1"/>
+    <col min="6389" max="6389" width="13.140625" style="2" customWidth="1"/>
+    <col min="6390" max="6394" width="9.140625" style="2"/>
+    <col min="6395" max="6395" width="10.85546875" style="2" customWidth="1"/>
+    <col min="6396" max="6396" width="23" style="2" bestFit="1" customWidth="1"/>
+    <col min="6397" max="6397" width="10.5703125" style="2" customWidth="1"/>
+    <col min="6398" max="6398" width="10.85546875" style="2" customWidth="1"/>
+    <col min="6399" max="6643" width="9.140625" style="2"/>
+    <col min="6644" max="6644" width="26.5703125" style="2" customWidth="1"/>
+    <col min="6645" max="6645" width="13.140625" style="2" customWidth="1"/>
+    <col min="6646" max="6650" width="9.140625" style="2"/>
+    <col min="6651" max="6651" width="10.85546875" style="2" customWidth="1"/>
+    <col min="6652" max="6652" width="23" style="2" bestFit="1" customWidth="1"/>
+    <col min="6653" max="6653" width="10.5703125" style="2" customWidth="1"/>
+    <col min="6654" max="6654" width="10.85546875" style="2" customWidth="1"/>
+    <col min="6655" max="6899" width="9.140625" style="2"/>
+    <col min="6900" max="6900" width="26.5703125" style="2" customWidth="1"/>
+    <col min="6901" max="6901" width="13.140625" style="2" customWidth="1"/>
+    <col min="6902" max="6906" width="9.140625" style="2"/>
+    <col min="6907" max="6907" width="10.85546875" style="2" customWidth="1"/>
+    <col min="6908" max="6908" width="23" style="2" bestFit="1" customWidth="1"/>
+    <col min="6909" max="6909" width="10.5703125" style="2" customWidth="1"/>
+    <col min="6910" max="6910" width="10.85546875" style="2" customWidth="1"/>
+    <col min="6911" max="7155" width="9.140625" style="2"/>
+    <col min="7156" max="7156" width="26.5703125" style="2" customWidth="1"/>
+    <col min="7157" max="7157" width="13.140625" style="2" customWidth="1"/>
+    <col min="7158" max="7162" width="9.140625" style="2"/>
+    <col min="7163" max="7163" width="10.85546875" style="2" customWidth="1"/>
+    <col min="7164" max="7164" width="23" style="2" bestFit="1" customWidth="1"/>
+    <col min="7165" max="7165" width="10.5703125" style="2" customWidth="1"/>
+    <col min="7166" max="7166" width="10.85546875" style="2" customWidth="1"/>
+    <col min="7167" max="7411" width="9.140625" style="2"/>
+    <col min="7412" max="7412" width="26.5703125" style="2" customWidth="1"/>
+    <col min="7413" max="7413" width="13.140625" style="2" customWidth="1"/>
+    <col min="7414" max="7418" width="9.140625" style="2"/>
+    <col min="7419" max="7419" width="10.85546875" style="2" customWidth="1"/>
+    <col min="7420" max="7420" width="23" style="2" bestFit="1" customWidth="1"/>
+    <col min="7421" max="7421" width="10.5703125" style="2" customWidth="1"/>
+    <col min="7422" max="7422" width="10.85546875" style="2" customWidth="1"/>
+    <col min="7423" max="7667" width="9.140625" style="2"/>
+    <col min="7668" max="7668" width="26.5703125" style="2" customWidth="1"/>
+    <col min="7669" max="7669" width="13.140625" style="2" customWidth="1"/>
+    <col min="7670" max="7674" width="9.140625" style="2"/>
+    <col min="7675" max="7675" width="10.85546875" style="2" customWidth="1"/>
+    <col min="7676" max="7676" width="23" style="2" bestFit="1" customWidth="1"/>
+    <col min="7677" max="7677" width="10.5703125" style="2" customWidth="1"/>
+    <col min="7678" max="7678" width="10.85546875" style="2" customWidth="1"/>
+    <col min="7679" max="7923" width="9.140625" style="2"/>
+    <col min="7924" max="7924" width="26.5703125" style="2" customWidth="1"/>
+    <col min="7925" max="7925" width="13.140625" style="2" customWidth="1"/>
+    <col min="7926" max="7930" width="9.140625" style="2"/>
+    <col min="7931" max="7931" width="10.85546875" style="2" customWidth="1"/>
+    <col min="7932" max="7932" width="23" style="2" bestFit="1" customWidth="1"/>
+    <col min="7933" max="7933" width="10.5703125" style="2" customWidth="1"/>
+    <col min="7934" max="7934" width="10.85546875" style="2" customWidth="1"/>
+    <col min="7935" max="8179" width="9.140625" style="2"/>
+    <col min="8180" max="8180" width="26.5703125" style="2" customWidth="1"/>
+    <col min="8181" max="8181" width="13.140625" style="2" customWidth="1"/>
+    <col min="8182" max="8186" width="9.140625" style="2"/>
+    <col min="8187" max="8187" width="10.85546875" style="2" customWidth="1"/>
+    <col min="8188" max="8188" width="23" style="2" bestFit="1" customWidth="1"/>
+    <col min="8189" max="8189" width="10.5703125" style="2" customWidth="1"/>
+    <col min="8190" max="8190" width="10.85546875" style="2" customWidth="1"/>
+    <col min="8191" max="8435" width="9.140625" style="2"/>
+    <col min="8436" max="8436" width="26.5703125" style="2" customWidth="1"/>
+    <col min="8437" max="8437" width="13.140625" style="2" customWidth="1"/>
+    <col min="8438" max="8442" width="9.140625" style="2"/>
+    <col min="8443" max="8443" width="10.85546875" style="2" customWidth="1"/>
+    <col min="8444" max="8444" width="23" style="2" bestFit="1" customWidth="1"/>
+    <col min="8445" max="8445" width="10.5703125" style="2" customWidth="1"/>
+    <col min="8446" max="8446" width="10.85546875" style="2" customWidth="1"/>
+    <col min="8447" max="8691" width="9.140625" style="2"/>
+    <col min="8692" max="8692" width="26.5703125" style="2" customWidth="1"/>
+    <col min="8693" max="8693" width="13.140625" style="2" customWidth="1"/>
+    <col min="8694" max="8698" width="9.140625" style="2"/>
+    <col min="8699" max="8699" width="10.85546875" style="2" customWidth="1"/>
+    <col min="8700" max="8700" width="23" style="2" bestFit="1" customWidth="1"/>
+    <col min="8701" max="8701" width="10.5703125" style="2" customWidth="1"/>
+    <col min="8702" max="8702" width="10.85546875" style="2" customWidth="1"/>
+    <col min="8703" max="8947" width="9.140625" style="2"/>
+    <col min="8948" max="8948" width="26.5703125" style="2" customWidth="1"/>
+    <col min="8949" max="8949" width="13.140625" style="2" customWidth="1"/>
+    <col min="8950" max="8954" width="9.140625" style="2"/>
+    <col min="8955" max="8955" width="10.85546875" style="2" customWidth="1"/>
+    <col min="8956" max="8956" width="23" style="2" bestFit="1" customWidth="1"/>
+    <col min="8957" max="8957" width="10.5703125" style="2" customWidth="1"/>
+    <col min="8958" max="8958" width="10.85546875" style="2" customWidth="1"/>
+    <col min="8959" max="9203" width="9.140625" style="2"/>
+    <col min="9204" max="9204" width="26.5703125" style="2" customWidth="1"/>
+    <col min="9205" max="9205" width="13.140625" style="2" customWidth="1"/>
+    <col min="9206" max="9210" width="9.140625" style="2"/>
+    <col min="9211" max="9211" width="10.85546875" style="2" customWidth="1"/>
+    <col min="9212" max="9212" width="23" style="2" bestFit="1" customWidth="1"/>
+    <col min="9213" max="9213" width="10.5703125" style="2" customWidth="1"/>
+    <col min="9214" max="9214" width="10.85546875" style="2" customWidth="1"/>
+    <col min="9215" max="9459" width="9.140625" style="2"/>
+    <col min="9460" max="9460" width="26.5703125" style="2" customWidth="1"/>
+    <col min="9461" max="9461" width="13.140625" style="2" customWidth="1"/>
+    <col min="9462" max="9466" width="9.140625" style="2"/>
+    <col min="9467" max="9467" width="10.85546875" style="2" customWidth="1"/>
+    <col min="9468" max="9468" width="23" style="2" bestFit="1" customWidth="1"/>
+    <col min="9469" max="9469" width="10.5703125" style="2" customWidth="1"/>
+    <col min="9470" max="9470" width="10.85546875" style="2" customWidth="1"/>
+    <col min="9471" max="9715" width="9.140625" style="2"/>
+    <col min="9716" max="9716" width="26.5703125" style="2" customWidth="1"/>
+    <col min="9717" max="9717" width="13.140625" style="2" customWidth="1"/>
+    <col min="9718" max="9722" width="9.140625" style="2"/>
+    <col min="9723" max="9723" width="10.85546875" style="2" customWidth="1"/>
+    <col min="9724" max="9724" width="23" style="2" bestFit="1" customWidth="1"/>
+    <col min="9725" max="9725" width="10.5703125" style="2" customWidth="1"/>
+    <col min="9726" max="9726" width="10.85546875" style="2" customWidth="1"/>
+    <col min="9727" max="9971" width="9.140625" style="2"/>
+    <col min="9972" max="9972" width="26.5703125" style="2" customWidth="1"/>
+    <col min="9973" max="9973" width="13.140625" style="2" customWidth="1"/>
+    <col min="9974" max="9978" width="9.140625" style="2"/>
+    <col min="9979" max="9979" width="10.85546875" style="2" customWidth="1"/>
+    <col min="9980" max="9980" width="23" style="2" bestFit="1" customWidth="1"/>
+    <col min="9981" max="9981" width="10.5703125" style="2" customWidth="1"/>
+    <col min="9982" max="9982" width="10.85546875" style="2" customWidth="1"/>
+    <col min="9983" max="10227" width="9.140625" style="2"/>
+    <col min="10228" max="10228" width="26.5703125" style="2" customWidth="1"/>
+    <col min="10229" max="10229" width="13.140625" style="2" customWidth="1"/>
+    <col min="10230" max="10234" width="9.140625" style="2"/>
+    <col min="10235" max="10235" width="10.85546875" style="2" customWidth="1"/>
+    <col min="10236" max="10236" width="23" style="2" bestFit="1" customWidth="1"/>
+    <col min="10237" max="10237" width="10.5703125" style="2" customWidth="1"/>
+    <col min="10238" max="10238" width="10.85546875" style="2" customWidth="1"/>
+    <col min="10239" max="10483" width="9.140625" style="2"/>
+    <col min="10484" max="10484" width="26.5703125" style="2" customWidth="1"/>
+    <col min="10485" max="10485" width="13.140625" style="2" customWidth="1"/>
+    <col min="10486" max="10490" width="9.140625" style="2"/>
+    <col min="10491" max="10491" width="10.85546875" style="2" customWidth="1"/>
+    <col min="10492" max="10492" width="23" style="2" bestFit="1" customWidth="1"/>
+    <col min="10493" max="10493" width="10.5703125" style="2" customWidth="1"/>
+    <col min="10494" max="10494" width="10.85546875" style="2" customWidth="1"/>
+    <col min="10495" max="10739" width="9.140625" style="2"/>
+    <col min="10740" max="10740" width="26.5703125" style="2" customWidth="1"/>
+    <col min="10741" max="10741" width="13.140625" style="2" customWidth="1"/>
+    <col min="10742" max="10746" width="9.140625" style="2"/>
+    <col min="10747" max="10747" width="10.85546875" style="2" customWidth="1"/>
+    <col min="10748" max="10748" width="23" style="2" bestFit="1" customWidth="1"/>
+    <col min="10749" max="10749" width="10.5703125" style="2" customWidth="1"/>
+    <col min="10750" max="10750" width="10.85546875" style="2" customWidth="1"/>
+    <col min="10751" max="10995" width="9.140625" style="2"/>
+    <col min="10996" max="10996" width="26.5703125" style="2" customWidth="1"/>
+    <col min="10997" max="10997" width="13.140625" style="2" customWidth="1"/>
+    <col min="10998" max="11002" width="9.140625" style="2"/>
+    <col min="11003" max="11003" width="10.85546875" style="2" customWidth="1"/>
+    <col min="11004" max="11004" width="23" style="2" bestFit="1" customWidth="1"/>
+    <col min="11005" max="11005" width="10.5703125" style="2" customWidth="1"/>
+    <col min="11006" max="11006" width="10.85546875" style="2" customWidth="1"/>
+    <col min="11007" max="11251" width="9.140625" style="2"/>
+    <col min="11252" max="11252" width="26.5703125" style="2" customWidth="1"/>
+    <col min="11253" max="11253" width="13.140625" style="2" customWidth="1"/>
+    <col min="11254" max="11258" width="9.140625" style="2"/>
+    <col min="11259" max="11259" width="10.85546875" style="2" customWidth="1"/>
+    <col min="11260" max="11260" width="23" style="2" bestFit="1" customWidth="1"/>
+    <col min="11261" max="11261" width="10.5703125" style="2" customWidth="1"/>
+    <col min="11262" max="11262" width="10.85546875" style="2" customWidth="1"/>
+    <col min="11263" max="11507" width="9.140625" style="2"/>
+    <col min="11508" max="11508" width="26.5703125" style="2" customWidth="1"/>
+    <col min="11509" max="11509" width="13.140625" style="2" customWidth="1"/>
+    <col min="11510" max="11514" width="9.140625" style="2"/>
+    <col min="11515" max="11515" width="10.85546875" style="2" customWidth="1"/>
+    <col min="11516" max="11516" width="23" style="2" bestFit="1" customWidth="1"/>
+    <col min="11517" max="11517" width="10.5703125" style="2" customWidth="1"/>
+    <col min="11518" max="11518" width="10.85546875" style="2" customWidth="1"/>
+    <col min="11519" max="11763" width="9.140625" style="2"/>
+    <col min="11764" max="11764" width="26.5703125" style="2" customWidth="1"/>
+    <col min="11765" max="11765" width="13.140625" style="2" customWidth="1"/>
+    <col min="11766" max="11770" width="9.140625" style="2"/>
+    <col min="11771" max="11771" width="10.85546875" style="2" customWidth="1"/>
+    <col min="11772" max="11772" width="23" style="2" bestFit="1" customWidth="1"/>
+    <col min="11773" max="11773" width="10.5703125" style="2" customWidth="1"/>
+    <col min="11774" max="11774" width="10.85546875" style="2" customWidth="1"/>
+    <col min="11775" max="12019" width="9.140625" style="2"/>
+    <col min="12020" max="12020" width="26.5703125" style="2" customWidth="1"/>
+    <col min="12021" max="12021" width="13.140625" style="2" customWidth="1"/>
+    <col min="12022" max="12026" width="9.140625" style="2"/>
+    <col min="12027" max="12027" width="10.85546875" style="2" customWidth="1"/>
+    <col min="12028" max="12028" width="23" style="2" bestFit="1" customWidth="1"/>
+    <col min="12029" max="12029" width="10.5703125" style="2" customWidth="1"/>
+    <col min="12030" max="12030" width="10.85546875" style="2" customWidth="1"/>
+    <col min="12031" max="12275" width="9.140625" style="2"/>
+    <col min="12276" max="12276" width="26.5703125" style="2" customWidth="1"/>
+    <col min="12277" max="12277" width="13.140625" style="2" customWidth="1"/>
+    <col min="12278" max="12282" width="9.140625" style="2"/>
+    <col min="12283" max="12283" width="10.85546875" style="2" customWidth="1"/>
+    <col min="12284" max="12284" width="23" style="2" bestFit="1" customWidth="1"/>
+    <col min="12285" max="12285" width="10.5703125" style="2" customWidth="1"/>
+    <col min="12286" max="12286" width="10.85546875" style="2" customWidth="1"/>
+    <col min="12287" max="12531" width="9.140625" style="2"/>
+    <col min="12532" max="12532" width="26.5703125" style="2" customWidth="1"/>
+    <col min="12533" max="12533" width="13.140625" style="2" customWidth="1"/>
+    <col min="12534" max="12538" width="9.140625" style="2"/>
+    <col min="12539" max="12539" width="10.85546875" style="2" customWidth="1"/>
+    <col min="12540" max="12540" width="23" style="2" bestFit="1" customWidth="1"/>
+    <col min="12541" max="12541" width="10.5703125" style="2" customWidth="1"/>
+    <col min="12542" max="12542" width="10.85546875" style="2" customWidth="1"/>
+    <col min="12543" max="12787" width="9.140625" style="2"/>
+    <col min="12788" max="12788" width="26.5703125" style="2" customWidth="1"/>
+    <col min="12789" max="12789" width="13.140625" style="2" customWidth="1"/>
+    <col min="12790" max="12794" width="9.140625" style="2"/>
+    <col min="12795" max="12795" width="10.85546875" style="2" customWidth="1"/>
+    <col min="12796" max="12796" width="23" style="2" bestFit="1" customWidth="1"/>
+    <col min="12797" max="12797" width="10.5703125" style="2" customWidth="1"/>
+    <col min="12798" max="12798" width="10.85546875" style="2" customWidth="1"/>
+    <col min="12799" max="13043" width="9.140625" style="2"/>
+    <col min="13044" max="13044" width="26.5703125" style="2" customWidth="1"/>
+    <col min="13045" max="13045" width="13.140625" style="2" customWidth="1"/>
+    <col min="13046" max="13050" width="9.140625" style="2"/>
+    <col min="13051" max="13051" width="10.85546875" style="2" customWidth="1"/>
+    <col min="13052" max="13052" width="23" style="2" bestFit="1" customWidth="1"/>
+    <col min="13053" max="13053" width="10.5703125" style="2" customWidth="1"/>
+    <col min="13054" max="13054" width="10.85546875" style="2" customWidth="1"/>
+    <col min="13055" max="13299" width="9.140625" style="2"/>
+    <col min="13300" max="13300" width="26.5703125" style="2" customWidth="1"/>
+    <col min="13301" max="13301" width="13.140625" style="2" customWidth="1"/>
+    <col min="13302" max="13306" width="9.140625" style="2"/>
+    <col min="13307" max="13307" width="10.85546875" style="2" customWidth="1"/>
+    <col min="13308" max="13308" width="23" style="2" bestFit="1" customWidth="1"/>
+    <col min="13309" max="13309" width="10.5703125" style="2" customWidth="1"/>
+    <col min="13310" max="13310" width="10.85546875" style="2" customWidth="1"/>
+    <col min="13311" max="13555" width="9.140625" style="2"/>
+    <col min="13556" max="13556" width="26.5703125" style="2" customWidth="1"/>
+    <col min="13557" max="13557" width="13.140625" style="2" customWidth="1"/>
+    <col min="13558" max="13562" width="9.140625" style="2"/>
+    <col min="13563" max="13563" width="10.85546875" style="2" customWidth="1"/>
+    <col min="13564" max="13564" width="23" style="2" bestFit="1" customWidth="1"/>
+    <col min="13565" max="13565" width="10.5703125" style="2" customWidth="1"/>
+    <col min="13566" max="13566" width="10.85546875" style="2" customWidth="1"/>
+    <col min="13567" max="13811" width="9.140625" style="2"/>
+    <col min="13812" max="13812" width="26.5703125" style="2" customWidth="1"/>
+    <col min="13813" max="13813" width="13.140625" style="2" customWidth="1"/>
+    <col min="13814" max="13818" width="9.140625" style="2"/>
+    <col min="13819" max="13819" width="10.85546875" style="2" customWidth="1"/>
+    <col min="13820" max="13820" width="23" style="2" bestFit="1" customWidth="1"/>
+    <col min="13821" max="13821" width="10.5703125" style="2" customWidth="1"/>
+    <col min="13822" max="13822" width="10.85546875" style="2" customWidth="1"/>
+    <col min="13823" max="14067" width="9.140625" style="2"/>
+    <col min="14068" max="14068" width="26.5703125" style="2" customWidth="1"/>
+    <col min="14069" max="14069" width="13.140625" style="2" customWidth="1"/>
+    <col min="14070" max="14074" width="9.140625" style="2"/>
+    <col min="14075" max="14075" width="10.85546875" style="2" customWidth="1"/>
+    <col min="14076" max="14076" width="23" style="2" bestFit="1" customWidth="1"/>
+    <col min="14077" max="14077" width="10.5703125" style="2" customWidth="1"/>
+    <col min="14078" max="14078" width="10.85546875" style="2" customWidth="1"/>
+    <col min="14079" max="14323" width="9.140625" style="2"/>
+    <col min="14324" max="14324" width="26.5703125" style="2" customWidth="1"/>
+    <col min="14325" max="14325" width="13.140625" style="2" customWidth="1"/>
+    <col min="14326" max="14330" width="9.140625" style="2"/>
+    <col min="14331" max="14331" width="10.85546875" style="2" customWidth="1"/>
+    <col min="14332" max="14332" width="23" style="2" bestFit="1" customWidth="1"/>
+    <col min="14333" max="14333" width="10.5703125" style="2" customWidth="1"/>
+    <col min="14334" max="14334" width="10.85546875" style="2" customWidth="1"/>
+    <col min="14335" max="14579" width="9.140625" style="2"/>
+    <col min="14580" max="14580" width="26.5703125" style="2" customWidth="1"/>
+    <col min="14581" max="14581" width="13.140625" style="2" customWidth="1"/>
+    <col min="14582" max="14586" width="9.140625" style="2"/>
+    <col min="14587" max="14587" width="10.85546875" style="2" customWidth="1"/>
+    <col min="14588" max="14588" width="23" style="2" bestFit="1" customWidth="1"/>
+    <col min="14589" max="14589" width="10.5703125" style="2" customWidth="1"/>
+    <col min="14590" max="14590" width="10.85546875" style="2" customWidth="1"/>
+    <col min="14591" max="14835" width="9.140625" style="2"/>
+    <col min="14836" max="14836" width="26.5703125" style="2" customWidth="1"/>
+    <col min="14837" max="14837" width="13.140625" style="2" customWidth="1"/>
+    <col min="14838" max="14842" width="9.140625" style="2"/>
+    <col min="14843" max="14843" width="10.85546875" style="2" customWidth="1"/>
+    <col min="14844" max="14844" width="23" style="2" bestFit="1" customWidth="1"/>
+    <col min="14845" max="14845" width="10.5703125" style="2" customWidth="1"/>
+    <col min="14846" max="14846" width="10.85546875" style="2" customWidth="1"/>
+    <col min="14847" max="15091" width="9.140625" style="2"/>
+    <col min="15092" max="15092" width="26.5703125" style="2" customWidth="1"/>
+    <col min="15093" max="15093" width="13.140625" style="2" customWidth="1"/>
+    <col min="15094" max="15098" width="9.140625" style="2"/>
+    <col min="15099" max="15099" width="10.85546875" style="2" customWidth="1"/>
+    <col min="15100" max="15100" width="23" style="2" bestFit="1" customWidth="1"/>
+    <col min="15101" max="15101" width="10.5703125" style="2" customWidth="1"/>
+    <col min="15102" max="15102" width="10.85546875" style="2" customWidth="1"/>
+    <col min="15103" max="15347" width="9.140625" style="2"/>
+    <col min="15348" max="15348" width="26.5703125" style="2" customWidth="1"/>
+    <col min="15349" max="15349" width="13.140625" style="2" customWidth="1"/>
+    <col min="15350" max="15354" width="9.140625" style="2"/>
+    <col min="15355" max="15355" width="10.85546875" style="2" customWidth="1"/>
+    <col min="15356" max="15356" width="23" style="2" bestFit="1" customWidth="1"/>
+    <col min="15357" max="15357" width="10.5703125" style="2" customWidth="1"/>
+    <col min="15358" max="15358" width="10.85546875" style="2" customWidth="1"/>
+    <col min="15359" max="15603" width="9.140625" style="2"/>
+    <col min="15604" max="15604" width="26.5703125" style="2" customWidth="1"/>
+    <col min="15605" max="15605" width="13.140625" style="2" customWidth="1"/>
+    <col min="15606" max="15610" width="9.140625" style="2"/>
+    <col min="15611" max="15611" width="10.85546875" style="2" customWidth="1"/>
+    <col min="15612" max="15612" width="23" style="2" bestFit="1" customWidth="1"/>
+    <col min="15613" max="15613" width="10.5703125" style="2" customWidth="1"/>
+    <col min="15614" max="15614" width="10.85546875" style="2" customWidth="1"/>
+    <col min="15615" max="15859" width="9.140625" style="2"/>
+    <col min="15860" max="15860" width="26.5703125" style="2" customWidth="1"/>
+    <col min="15861" max="15861" width="13.140625" style="2" customWidth="1"/>
+    <col min="15862" max="15866" width="9.140625" style="2"/>
+    <col min="15867" max="15867" width="10.85546875" style="2" customWidth="1"/>
+    <col min="15868" max="15868" width="23" style="2" bestFit="1" customWidth="1"/>
+    <col min="15869" max="15869" width="10.5703125" style="2" customWidth="1"/>
+    <col min="15870" max="15870" width="10.85546875" style="2" customWidth="1"/>
+    <col min="15871" max="16115" width="9.140625" style="2"/>
+    <col min="16116" max="16116" width="26.5703125" style="2" customWidth="1"/>
+    <col min="16117" max="16117" width="13.140625" style="2" customWidth="1"/>
+    <col min="16118" max="16122" width="9.140625" style="2"/>
+    <col min="16123" max="16123" width="10.85546875" style="2" customWidth="1"/>
+    <col min="16124" max="16124" width="23" style="2" bestFit="1" customWidth="1"/>
+    <col min="16125" max="16125" width="10.5703125" style="2" customWidth="1"/>
+    <col min="16126" max="16126" width="10.85546875" style="2" customWidth="1"/>
+    <col min="16127" max="16384" width="9.140625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="30" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="30" t="s">
+        <v>47</v>
+      </c>
+      <c r="E3" s="31"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B4" s="6">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B5" s="32">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B6" s="40">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B8" s="33">
+        <v>1</v>
+      </c>
+      <c r="C8" s="33">
+        <v>2</v>
+      </c>
+      <c r="D8" s="33">
+        <v>3</v>
+      </c>
+      <c r="E8" s="33">
+        <v>4</v>
+      </c>
+      <c r="F8" s="33">
+        <v>5</v>
+      </c>
+      <c r="G8" s="33">
+        <v>6</v>
+      </c>
+      <c r="H8" s="34"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="35" t="s">
+        <v>51</v>
+      </c>
+      <c r="B9" s="36">
+        <v>12.5</v>
+      </c>
+      <c r="C9" s="36">
+        <v>12.55</v>
+      </c>
+      <c r="D9" s="36">
+        <v>12.7</v>
+      </c>
+      <c r="E9" s="36">
+        <v>12.8</v>
+      </c>
+      <c r="F9" s="36">
+        <v>12.85</v>
+      </c>
+      <c r="G9" s="36">
+        <v>12.95</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="35" t="s">
+        <v>52</v>
+      </c>
+      <c r="B10" s="37">
+        <f>B9*0.05</f>
+        <v>0.625</v>
+      </c>
+      <c r="C10" s="37">
+        <f t="shared" ref="C10:G10" si="0">C9*0.05</f>
+        <v>0.62750000000000006</v>
+      </c>
+      <c r="D10" s="37">
+        <f t="shared" si="0"/>
+        <v>0.63500000000000001</v>
+      </c>
+      <c r="E10" s="37">
+        <f t="shared" si="0"/>
+        <v>0.64000000000000012</v>
+      </c>
+      <c r="F10" s="37">
+        <f t="shared" si="0"/>
+        <v>0.64250000000000007</v>
+      </c>
+      <c r="G10" s="37">
+        <f t="shared" si="0"/>
+        <v>0.64749999999999996</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B12" s="33">
+        <v>1</v>
+      </c>
+      <c r="C12" s="33">
+        <v>2</v>
+      </c>
+      <c r="D12" s="33">
+        <v>3</v>
+      </c>
+      <c r="E12" s="33">
+        <v>4</v>
+      </c>
+      <c r="F12" s="33">
+        <v>5</v>
+      </c>
+      <c r="G12" s="33">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="19">
+        <v>5000</v>
+      </c>
+      <c r="C13" s="19">
+        <v>20000</v>
+      </c>
+      <c r="D13" s="19">
+        <v>30000</v>
+      </c>
+      <c r="E13" s="19">
+        <v>30000</v>
+      </c>
+      <c r="F13" s="19">
+        <v>25000</v>
+      </c>
+      <c r="G13" s="19">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B14" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="G14" s="11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B15" s="6">
+        <v>30000</v>
+      </c>
+      <c r="C15" s="6">
+        <v>30000</v>
+      </c>
+      <c r="D15" s="6">
+        <v>30000</v>
+      </c>
+      <c r="E15" s="6">
+        <v>30000</v>
+      </c>
+      <c r="F15" s="6">
+        <v>30000</v>
+      </c>
+      <c r="G15" s="6">
+        <v>30000</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" s="25" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B19" s="6">
+        <v>10000</v>
+      </c>
+      <c r="C19" s="6">
+        <v>15000</v>
+      </c>
+      <c r="D19" s="6">
+        <v>30000</v>
+      </c>
+      <c r="E19" s="6">
+        <v>35000</v>
+      </c>
+      <c r="F19" s="6">
+        <v>25000</v>
+      </c>
+      <c r="G19" s="6">
+        <v>10000</v>
+      </c>
+      <c r="H19" s="2">
+        <f>SUM(B19:G19)</f>
+        <v>125000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B20" s="11"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="11"/>
+      <c r="G20" s="11"/>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B21" s="12">
+        <f>$B$4 + B13- B19</f>
+        <v>0</v>
+      </c>
+      <c r="C21" s="12">
+        <f>B21 + C13- C19</f>
+        <v>5000</v>
+      </c>
+      <c r="D21" s="12">
+        <f t="shared" ref="D21:F21" si="1">C21 + D13- D19</f>
+        <v>5000</v>
+      </c>
+      <c r="E21" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F21" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G21" s="12">
+        <f>F21 + G13- G19</f>
+        <v>0</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B22" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B23" s="6">
+        <v>10000</v>
+      </c>
+      <c r="C23" s="6">
+        <v>10000</v>
+      </c>
+      <c r="D23" s="6">
+        <v>10000</v>
+      </c>
+      <c r="E23" s="6">
+        <v>10000</v>
+      </c>
+      <c r="F23" s="6">
+        <v>10000</v>
+      </c>
+      <c r="G23" s="6">
+        <v>10000</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A24" s="4"/>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B25" s="37"/>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B26" s="33">
+        <v>1</v>
+      </c>
+      <c r="C26" s="33">
+        <v>2</v>
+      </c>
+      <c r="D26" s="33">
+        <v>3</v>
+      </c>
+      <c r="E26" s="33">
+        <v>4</v>
+      </c>
+      <c r="F26" s="33">
+        <v>5</v>
+      </c>
+      <c r="G26" s="33">
+        <v>6</v>
+      </c>
+      <c r="H26" s="5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="H27" s="38">
+        <f>SUMPRODUCT(B10:G10, B21:G21)</f>
+        <v>6312.5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="H28" s="38">
+        <f>SUMPRODUCT(B9:G9,B13:G13)</f>
+        <v>1529250</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H29" s="39">
+        <f>SUM(H27:H28)</f>
+        <v>1535562.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/HW4/result/HW4.xlsx
+++ b/HW4/result/HW4.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\T00229\Documents\GitHub\DADS7102\HW4\result\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nuna\Documents\GitHub\DADS7102\HW4\result\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A823F48C-8B75-48C0-BEE2-64278D99B454}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A0BC3CA-6C16-47C3-8E9D-D48D7234A5CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4125" yWindow="2355" windowWidth="21600" windowHeight="11295" activeTab="2" xr2:uid="{34DA60CE-96CD-40DE-89EC-63BE59E8EFBC}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{34DA60CE-96CD-40DE-89EC-63BE59E8EFBC}"/>
   </bookViews>
   <sheets>
     <sheet name="FixedCost" sheetId="1" r:id="rId1"/>
@@ -23,39 +23,39 @@
   </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">CapitalBudget!$A$21:$J$149</definedName>
-    <definedName name="AFinish" localSheetId="2">[2]project!$K$6</definedName>
-    <definedName name="AFinish">[1]project!$K$6</definedName>
-    <definedName name="BFinish" localSheetId="2">[2]project!$K$7</definedName>
-    <definedName name="BFinish">[1]project!$K$7</definedName>
-    <definedName name="CFinish" localSheetId="2">[2]project!$K$8</definedName>
-    <definedName name="CFinish">[1]project!$K$8</definedName>
-    <definedName name="DFinish" localSheetId="2">[2]project!$K$9</definedName>
-    <definedName name="DFinish">[1]project!$K$9</definedName>
-    <definedName name="EFinish" localSheetId="2">[2]project!$K$10</definedName>
-    <definedName name="EFinish">[1]project!$K$10</definedName>
-    <definedName name="FFinish" localSheetId="2">[2]project!$K$11</definedName>
-    <definedName name="FFinish">[1]project!$K$11</definedName>
-    <definedName name="GFinish" localSheetId="2">[2]project!$K$12</definedName>
-    <definedName name="GFinish">[1]project!$K$12</definedName>
-    <definedName name="HFinish" localSheetId="2">[2]project!$K$13</definedName>
-    <definedName name="HFinish">[1]project!$K$13</definedName>
-    <definedName name="IFinish" localSheetId="2">[2]project!$K$14</definedName>
-    <definedName name="IFinish">[1]project!$K$14</definedName>
-    <definedName name="invLevels" localSheetId="2">[2]CapitalBudget!$B$10:$H$10</definedName>
-    <definedName name="invLevels">[1]CapitalBudget!$B$10:$H$10</definedName>
-    <definedName name="JFinish" localSheetId="2">[2]project!$K$15</definedName>
-    <definedName name="JFinish">[1]project!$K$15</definedName>
-    <definedName name="KFinish" localSheetId="2">[2]project!$K$16</definedName>
-    <definedName name="KFinish">[1]project!$K$16</definedName>
-    <definedName name="LFinish" localSheetId="2">[2]project!$K$17</definedName>
-    <definedName name="LFinish">[1]project!$K$17</definedName>
-    <definedName name="MFinish" localSheetId="2">[2]project!$K$18</definedName>
-    <definedName name="MFinish">[1]project!$K$18</definedName>
-    <definedName name="NFinish" localSheetId="2">[2]project!$K$19</definedName>
-    <definedName name="NFinish">[1]project!$K$19</definedName>
+    <definedName name="AFinish" localSheetId="2">[1]project!$K$6</definedName>
+    <definedName name="AFinish">[2]project!$K$6</definedName>
+    <definedName name="BFinish" localSheetId="2">[1]project!$K$7</definedName>
+    <definedName name="BFinish">[2]project!$K$7</definedName>
+    <definedName name="CFinish" localSheetId="2">[1]project!$K$8</definedName>
+    <definedName name="CFinish">[2]project!$K$8</definedName>
+    <definedName name="DFinish" localSheetId="2">[1]project!$K$9</definedName>
+    <definedName name="DFinish">[2]project!$K$9</definedName>
+    <definedName name="EFinish" localSheetId="2">[1]project!$K$10</definedName>
+    <definedName name="EFinish">[2]project!$K$10</definedName>
+    <definedName name="FFinish" localSheetId="2">[1]project!$K$11</definedName>
+    <definedName name="FFinish">[2]project!$K$11</definedName>
+    <definedName name="GFinish" localSheetId="2">[1]project!$K$12</definedName>
+    <definedName name="GFinish">[2]project!$K$12</definedName>
+    <definedName name="HFinish" localSheetId="2">[1]project!$K$13</definedName>
+    <definedName name="HFinish">[2]project!$K$13</definedName>
+    <definedName name="IFinish" localSheetId="2">[1]project!$K$14</definedName>
+    <definedName name="IFinish">[2]project!$K$14</definedName>
+    <definedName name="invLevels" localSheetId="2">[1]CapitalBudget!$B$10:$H$10</definedName>
+    <definedName name="invLevels">[2]CapitalBudget!$B$10:$H$10</definedName>
+    <definedName name="JFinish" localSheetId="2">[1]project!$K$15</definedName>
+    <definedName name="JFinish">[2]project!$K$15</definedName>
+    <definedName name="KFinish" localSheetId="2">[1]project!$K$16</definedName>
+    <definedName name="KFinish">[2]project!$K$16</definedName>
+    <definedName name="LFinish" localSheetId="2">[1]project!$K$17</definedName>
+    <definedName name="LFinish">[2]project!$K$17</definedName>
+    <definedName name="MFinish" localSheetId="2">[1]project!$K$18</definedName>
+    <definedName name="MFinish">[2]project!$K$18</definedName>
+    <definedName name="NFinish" localSheetId="2">[1]project!$K$19</definedName>
+    <definedName name="NFinish">[2]project!$K$19</definedName>
     <definedName name="solver_adj" localSheetId="1" hidden="1">CapitalBudget!$B$10:$H$10</definedName>
     <definedName name="solver_adj" localSheetId="0" hidden="1">FixedCost!$B$14:$G$15</definedName>
-    <definedName name="solver_adj" localSheetId="2" hidden="1">ProdPlanning!$B$13:$G$13</definedName>
+    <definedName name="solver_adj" localSheetId="2" hidden="1">ProdPlanning!$B$16:$G$17</definedName>
     <definedName name="solver_cvg" localSheetId="1" hidden="1">0.0001</definedName>
     <definedName name="solver_cvg" localSheetId="0" hidden="1">0.0001</definedName>
     <definedName name="solver_cvg" localSheetId="2" hidden="1">0.0001</definedName>
@@ -73,13 +73,13 @@
     <definedName name="solver_itr" localSheetId="2" hidden="1">2147483647</definedName>
     <definedName name="solver_lhs1" localSheetId="1" hidden="1">CapitalBudget!$B$14</definedName>
     <definedName name="solver_lhs1" localSheetId="0" hidden="1">FixedCost!$B$14:$G$14</definedName>
-    <definedName name="solver_lhs1" localSheetId="2" hidden="1">ProdPlanning!$B$13:$G$13</definedName>
+    <definedName name="solver_lhs1" localSheetId="2" hidden="1">ProdPlanning!$B$16:$G$16</definedName>
     <definedName name="solver_lhs2" localSheetId="1" hidden="1">CapitalBudget!$B$10:$H$10</definedName>
     <definedName name="solver_lhs2" localSheetId="0" hidden="1">FixedCost!$B$15:$G$15</definedName>
-    <definedName name="solver_lhs2" localSheetId="2" hidden="1">ProdPlanning!$B$21:$G$21</definedName>
+    <definedName name="solver_lhs2" localSheetId="2" hidden="1">ProdPlanning!$B$17:$G$17</definedName>
     <definedName name="solver_lhs3" localSheetId="1" hidden="1">CapitalBudget!$C$15</definedName>
     <definedName name="solver_lhs3" localSheetId="0" hidden="1">FixedCost!$B$23:$B$24</definedName>
-    <definedName name="solver_lhs3" localSheetId="2" hidden="1">ProdPlanning!$B$21:$G$21</definedName>
+    <definedName name="solver_lhs3" localSheetId="2" hidden="1">ProdPlanning!$B$27:$G$27</definedName>
     <definedName name="solver_lhs4" localSheetId="1" hidden="1">CapitalBudget!$B$10:$H$10</definedName>
     <definedName name="solver_lhs4" localSheetId="0" hidden="1">FixedCost!$B$23:$B$24</definedName>
     <definedName name="solver_lhs5" localSheetId="1" hidden="1">CapitalBudget!$B$10:$H$10</definedName>
@@ -109,7 +109,7 @@
     <definedName name="solver_nwt" localSheetId="2" hidden="1">1</definedName>
     <definedName name="solver_opt" localSheetId="1" hidden="1">CapitalBudget!$B$17</definedName>
     <definedName name="solver_opt" localSheetId="0" hidden="1">FixedCost!$B$30</definedName>
-    <definedName name="solver_opt" localSheetId="2" hidden="1">ProdPlanning!$H$29</definedName>
+    <definedName name="solver_opt" localSheetId="2" hidden="1">ProdPlanning!$H$36</definedName>
     <definedName name="solver_pre" localSheetId="1" hidden="1">0.000001</definedName>
     <definedName name="solver_pre" localSheetId="0" hidden="1">0.000001</definedName>
     <definedName name="solver_pre" localSheetId="2" hidden="1">0.000001</definedName>
@@ -118,7 +118,7 @@
     <definedName name="solver_rbv" localSheetId="2" hidden="1">1</definedName>
     <definedName name="solver_rel1" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_rel1" localSheetId="0" hidden="1">5</definedName>
-    <definedName name="solver_rel1" localSheetId="2" hidden="1">1</definedName>
+    <definedName name="solver_rel1" localSheetId="2" hidden="1">5</definedName>
     <definedName name="solver_rel2" localSheetId="1" hidden="1">5</definedName>
     <definedName name="solver_rel2" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_rel2" localSheetId="2" hidden="1">1</definedName>
@@ -130,10 +130,10 @@
     <definedName name="solver_rel5" localSheetId="1" hidden="1">5</definedName>
     <definedName name="solver_rhs1" localSheetId="1" hidden="1">CapitalBudget!$D$14</definedName>
     <definedName name="solver_rhs1" localSheetId="0" hidden="1">"binary"</definedName>
-    <definedName name="solver_rhs1" localSheetId="2" hidden="1">ProdPlanning!$B$15:$G$15</definedName>
+    <definedName name="solver_rhs1" localSheetId="2" hidden="1">"binary"</definedName>
     <definedName name="solver_rhs2" localSheetId="1" hidden="1">"binary"</definedName>
     <definedName name="solver_rhs2" localSheetId="0" hidden="1">FixedCost!$B$17:$G$17</definedName>
-    <definedName name="solver_rhs2" localSheetId="2" hidden="1">ProdPlanning!$B$23:$G$23</definedName>
+    <definedName name="solver_rhs2" localSheetId="2" hidden="1">ProdPlanning!$B$19:$G$19</definedName>
     <definedName name="solver_rhs3" localSheetId="1" hidden="1">0</definedName>
     <definedName name="solver_rhs3" localSheetId="0" hidden="1">FixedCost!$D$23:$D$24</definedName>
     <definedName name="solver_rhs3" localSheetId="2" hidden="1">0</definedName>
@@ -160,7 +160,7 @@
     <definedName name="solver_tim" localSheetId="2" hidden="1">2147483647</definedName>
     <definedName name="solver_tol" localSheetId="1" hidden="1">0.01</definedName>
     <definedName name="solver_tol" localSheetId="0" hidden="1">0.01</definedName>
-    <definedName name="solver_tol" localSheetId="2" hidden="1">0.01</definedName>
+    <definedName name="solver_tol" localSheetId="2" hidden="1">0</definedName>
     <definedName name="solver_typ" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_typ" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_typ" localSheetId="2" hidden="1">2</definedName>
@@ -249,7 +249,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="74">
   <si>
     <t>Great Threads fixed cost clothing model</t>
   </si>
@@ -454,12 +454,30 @@
   <si>
     <t>fixed setup cost</t>
   </si>
+  <si>
+    <t>Produce Any</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>fixed cost/month</t>
+  </si>
+  <si>
+    <t>W</t>
+  </si>
+  <si>
+    <t>fixed cost</t>
+  </si>
+  <si>
+    <t>M * yt</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="11">
+  <numFmts count="12">
     <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
     <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
@@ -470,7 +488,8 @@
     <numFmt numFmtId="168" formatCode="0.0000"/>
     <numFmt numFmtId="169" formatCode="0.000"/>
     <numFmt numFmtId="170" formatCode="&quot;$&quot;#,##0.000_);\(&quot;$&quot;#,##0.000\)"/>
-    <numFmt numFmtId="174" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="171" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="172" formatCode="&quot;$&quot;#,##0"/>
   </numFmts>
   <fonts count="10" x14ac:knownFonts="1">
     <font>
@@ -540,7 +559,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -573,7 +592,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.79998168889431442"/>
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1" tint="0.34998626667073579"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -628,7 +659,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="8" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -701,9 +732,27 @@
     </xf>
     <xf numFmtId="8" fontId="4" fillId="2" borderId="0" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="170" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" xfId="4" applyFont="1"/>
-    <xf numFmtId="43" fontId="4" fillId="6" borderId="2" xfId="4" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="174" fontId="4" fillId="2" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="2" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="171" fontId="4" fillId="2" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="171" fontId="4" fillId="6" borderId="2" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="4" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="171" fontId="4" fillId="2" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="172" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="43" fontId="4" fillId="8" borderId="0" xfId="4" applyFont="1" applyFill="1"/>
+    <xf numFmtId="171" fontId="4" fillId="8" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Comma" xfId="4" builtinId="3"/>
@@ -727,7 +776,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Sensitivity Report 1"/>
@@ -766,13 +815,13 @@
       <sheetName val="Location"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
       <sheetData sheetId="7"/>
       <sheetData sheetId="8">
         <row r="6">
@@ -846,17 +895,17 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
-      <sheetData sheetId="13"/>
-      <sheetData sheetId="14"/>
-      <sheetData sheetId="15"/>
-      <sheetData sheetId="16"/>
-      <sheetData sheetId="17"/>
-      <sheetData sheetId="18"/>
-      <sheetData sheetId="19"/>
+      <sheetData sheetId="9" refreshError="1"/>
+      <sheetData sheetId="10" refreshError="1"/>
+      <sheetData sheetId="11" refreshError="1"/>
+      <sheetData sheetId="12" refreshError="1"/>
+      <sheetData sheetId="13" refreshError="1"/>
+      <sheetData sheetId="14" refreshError="1"/>
+      <sheetData sheetId="15" refreshError="1"/>
+      <sheetData sheetId="16" refreshError="1"/>
+      <sheetData sheetId="17" refreshError="1"/>
+      <sheetData sheetId="18" refreshError="1"/>
+      <sheetData sheetId="19" refreshError="1"/>
       <sheetData sheetId="20">
         <row r="10">
           <cell r="B10">
@@ -882,27 +931,30 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="21"/>
-      <sheetData sheetId="22"/>
-      <sheetData sheetId="23"/>
-      <sheetData sheetId="24"/>
-      <sheetData sheetId="25"/>
-      <sheetData sheetId="26"/>
-      <sheetData sheetId="27"/>
-      <sheetData sheetId="28"/>
-      <sheetData sheetId="29"/>
-      <sheetData sheetId="30"/>
-      <sheetData sheetId="31"/>
-      <sheetData sheetId="32"/>
-      <sheetData sheetId="33"/>
+      <sheetData sheetId="21" refreshError="1"/>
+      <sheetData sheetId="22" refreshError="1"/>
+      <sheetData sheetId="23" refreshError="1"/>
+      <sheetData sheetId="24" refreshError="1"/>
+      <sheetData sheetId="25" refreshError="1"/>
+      <sheetData sheetId="26" refreshError="1"/>
+      <sheetData sheetId="27" refreshError="1"/>
+      <sheetData sheetId="28" refreshError="1"/>
+      <sheetData sheetId="29" refreshError="1"/>
+      <sheetData sheetId="30" refreshError="1"/>
+      <sheetData sheetId="31" refreshError="1"/>
+      <sheetData sheetId="32" refreshError="1"/>
+      <sheetData sheetId="33" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
 </file>
 
 <file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Sensitivity Report 1"/>
       <sheetName val="ProductMix"/>
@@ -947,7 +999,7 @@
       <sheetData sheetId="4" refreshError="1"/>
       <sheetData sheetId="5" refreshError="1"/>
       <sheetData sheetId="6" refreshError="1"/>
-      <sheetData sheetId="7"/>
+      <sheetData sheetId="7" refreshError="1"/>
       <sheetData sheetId="8">
         <row r="6">
           <cell r="K6">
@@ -7777,14 +7829,14 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87743ED0-3CDD-4FFA-AF50-C4DAE5D2AEAC}">
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28.5703125" style="2" customWidth="1"/>
     <col min="2" max="2" width="13.140625" style="2" customWidth="1"/>
-    <col min="3" max="7" width="9.140625" style="2"/>
+    <col min="3" max="7" width="10.5703125" style="2" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.42578125" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="243" width="9.140625" style="2"/>
     <col min="244" max="244" width="26.5703125" style="2" customWidth="1"/>
     <col min="245" max="245" width="13.140625" style="2" customWidth="1"/>
@@ -8292,18 +8344,18 @@
     <col min="16127" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="30" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="30" t="s">
         <v>47</v>
       </c>
       <c r="E3" s="31"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>48</v>
       </c>
@@ -8311,7 +8363,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>49</v>
       </c>
@@ -8319,373 +8371,526 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="B6" s="40">
+      <c r="B6" s="41">
         <v>15000</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B7" s="44">
+        <f>SUM(B25:G25)</f>
+        <v>125000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B8" s="33">
-        <v>1</v>
-      </c>
-      <c r="C8" s="33">
+      <c r="B9" s="33">
+        <v>1</v>
+      </c>
+      <c r="C9" s="33">
         <v>2</v>
       </c>
-      <c r="D8" s="33">
+      <c r="D9" s="33">
         <v>3</v>
       </c>
-      <c r="E8" s="33">
+      <c r="E9" s="33">
         <v>4</v>
       </c>
-      <c r="F8" s="33">
+      <c r="F9" s="33">
         <v>5</v>
       </c>
-      <c r="G8" s="33">
+      <c r="G9" s="33">
         <v>6</v>
       </c>
-      <c r="H8" s="34"/>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="35" t="s">
+      <c r="H9" s="34"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="35" t="s">
         <v>51</v>
       </c>
-      <c r="B9" s="36">
+      <c r="B10" s="36">
         <v>12.5</v>
       </c>
-      <c r="C9" s="36">
+      <c r="C10" s="36">
         <v>12.55</v>
       </c>
-      <c r="D9" s="36">
+      <c r="D10" s="36">
         <v>12.7</v>
       </c>
-      <c r="E9" s="36">
+      <c r="E10" s="36">
         <v>12.8</v>
       </c>
-      <c r="F9" s="36">
+      <c r="F10" s="36">
         <v>12.85</v>
       </c>
-      <c r="G9" s="36">
+      <c r="G10" s="36">
         <v>12.95</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="35" t="s">
+      <c r="H10" s="34"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="35" t="s">
         <v>52</v>
       </c>
-      <c r="B10" s="37">
-        <f>B9*0.05</f>
+      <c r="B11" s="37">
+        <f>B10*0.05</f>
         <v>0.625</v>
       </c>
-      <c r="C10" s="37">
-        <f t="shared" ref="C10:G10" si="0">C9*0.05</f>
+      <c r="C11" s="37">
+        <f t="shared" ref="C11:G11" si="0">C10*0.05</f>
         <v>0.62750000000000006</v>
       </c>
-      <c r="D10" s="37">
+      <c r="D11" s="37">
         <f t="shared" si="0"/>
         <v>0.63500000000000001</v>
       </c>
-      <c r="E10" s="37">
+      <c r="E11" s="37">
         <f t="shared" si="0"/>
         <v>0.64000000000000012</v>
       </c>
-      <c r="F10" s="37">
+      <c r="F11" s="37">
         <f t="shared" si="0"/>
         <v>0.64250000000000007</v>
       </c>
-      <c r="G10" s="37">
+      <c r="G11" s="37">
         <f t="shared" si="0"/>
         <v>0.64749999999999996</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B12" s="45">
+        <f>$B$6</f>
+        <v>15000</v>
+      </c>
+      <c r="C12" s="45">
+        <f t="shared" ref="C12:F12" si="1">$B$6</f>
+        <v>15000</v>
+      </c>
+      <c r="D12" s="45">
+        <f t="shared" si="1"/>
+        <v>15000</v>
+      </c>
+      <c r="E12" s="45">
+        <f t="shared" si="1"/>
+        <v>15000</v>
+      </c>
+      <c r="F12" s="45">
+        <f t="shared" si="1"/>
+        <v>15000</v>
+      </c>
+      <c r="G12" s="45">
+        <f>$B$6</f>
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B13" s="33"/>
+      <c r="C13" s="33"/>
+      <c r="D13" s="33"/>
+      <c r="E13" s="33"/>
+      <c r="F13" s="33"/>
+      <c r="G13" s="33"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B12" s="33">
-        <v>1</v>
-      </c>
-      <c r="C12" s="33">
+      <c r="B15" s="33">
+        <v>1</v>
+      </c>
+      <c r="C15" s="33">
         <v>2</v>
       </c>
-      <c r="D12" s="33">
+      <c r="D15" s="33">
         <v>3</v>
       </c>
-      <c r="E12" s="33">
+      <c r="E15" s="33">
         <v>4</v>
       </c>
-      <c r="F12" s="33">
+      <c r="F15" s="33">
         <v>5</v>
       </c>
-      <c r="G12" s="33">
+      <c r="G15" s="33">
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B16" s="43">
+        <v>1</v>
+      </c>
+      <c r="C16" s="43">
+        <v>0</v>
+      </c>
+      <c r="D16" s="43">
+        <v>1</v>
+      </c>
+      <c r="E16" s="43">
+        <v>1</v>
+      </c>
+      <c r="F16" s="43">
+        <v>1</v>
+      </c>
+      <c r="G16" s="43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="19">
-        <v>5000</v>
-      </c>
-      <c r="C13" s="19">
+      <c r="B17" s="19">
         <v>20000</v>
       </c>
-      <c r="D13" s="19">
+      <c r="C17" s="19">
+        <v>0</v>
+      </c>
+      <c r="D17" s="19">
         <v>30000</v>
       </c>
-      <c r="E13" s="19">
-        <v>30000</v>
-      </c>
-      <c r="F13" s="19">
-        <v>25000</v>
-      </c>
-      <c r="G13" s="19">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B14" s="11" t="s">
+      <c r="E17" s="19">
+        <v>35000</v>
+      </c>
+      <c r="F17" s="19">
+        <v>35000</v>
+      </c>
+      <c r="G17" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B18" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="11" t="s">
+      <c r="C18" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D14" s="11" t="s">
+      <c r="D18" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E14" s="11" t="s">
+      <c r="E18" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="F14" s="11" t="s">
+      <c r="F18" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G14" s="11" t="s">
+      <c r="G18" s="5" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B15" s="6">
-        <v>30000</v>
-      </c>
-      <c r="C15" s="6">
-        <v>30000</v>
-      </c>
-      <c r="D15" s="6">
-        <v>30000</v>
-      </c>
-      <c r="E15" s="6">
-        <v>30000</v>
-      </c>
-      <c r="F15" s="6">
-        <v>30000</v>
-      </c>
-      <c r="G15" s="6">
-        <v>30000</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" s="25" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B18" s="5"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
-      <c r="G18" s="5"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B19" s="20">
+        <f>B16 * $B$7</f>
+        <v>125000</v>
+      </c>
+      <c r="C19" s="20">
+        <f t="shared" ref="C19:G19" si="2">C16 * $B$7</f>
+        <v>0</v>
+      </c>
+      <c r="D19" s="20">
+        <f t="shared" si="2"/>
+        <v>125000</v>
+      </c>
+      <c r="E19" s="20">
+        <f t="shared" si="2"/>
+        <v>125000</v>
+      </c>
+      <c r="F19" s="20">
+        <f t="shared" si="2"/>
+        <v>125000</v>
+      </c>
+      <c r="G19" s="20">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" s="38"/>
+      <c r="B20" s="40" t="s">
+        <v>17</v>
+      </c>
+      <c r="C20" s="40" t="s">
+        <v>17</v>
+      </c>
+      <c r="D20" s="40" t="s">
+        <v>17</v>
+      </c>
+      <c r="E20" s="40" t="s">
+        <v>17</v>
+      </c>
+      <c r="F20" s="40" t="s">
+        <v>17</v>
+      </c>
+      <c r="G20" s="40" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" s="38" t="s">
+        <v>54</v>
+      </c>
+      <c r="B21" s="38">
+        <v>30000</v>
+      </c>
+      <c r="C21" s="38">
+        <v>30000</v>
+      </c>
+      <c r="D21" s="38">
+        <v>30000</v>
+      </c>
+      <c r="E21" s="38">
+        <v>30000</v>
+      </c>
+      <c r="F21" s="38">
+        <v>30000</v>
+      </c>
+      <c r="G21" s="38">
+        <v>30000</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H22" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23" s="25" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B24" s="5"/>
+      <c r="C24" s="5"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5"/>
+      <c r="G24" s="5"/>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="B19" s="6">
+      <c r="B25" s="6">
         <v>10000</v>
       </c>
-      <c r="C19" s="6">
+      <c r="C25" s="6">
         <v>15000</v>
       </c>
-      <c r="D19" s="6">
+      <c r="D25" s="6">
         <v>30000</v>
       </c>
-      <c r="E19" s="6">
+      <c r="E25" s="6">
         <v>35000</v>
       </c>
-      <c r="F19" s="6">
+      <c r="F25" s="6">
         <v>25000</v>
       </c>
-      <c r="G19" s="6">
+      <c r="G25" s="6">
         <v>10000</v>
       </c>
-      <c r="H19" s="2">
-        <f>SUM(B19:G19)</f>
+      <c r="H25" s="2">
+        <f>SUM(B25:G25)</f>
         <v>125000</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B20" s="11"/>
-      <c r="C20" s="11"/>
-      <c r="D20" s="11"/>
-      <c r="E20" s="11"/>
-      <c r="F20" s="11"/>
-      <c r="G20" s="11"/>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B21" s="12">
-        <f>$B$4 + B13- B19</f>
-        <v>0</v>
-      </c>
-      <c r="C21" s="12">
-        <f>B21 + C13- C19</f>
-        <v>5000</v>
-      </c>
-      <c r="D21" s="12">
-        <f t="shared" ref="D21:F21" si="1">C21 + D13- D19</f>
-        <v>5000</v>
-      </c>
-      <c r="E21" s="12">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F21" s="12">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G21" s="12">
-        <f>F21 + G13- G19</f>
-        <v>0</v>
-      </c>
-      <c r="H21" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B22" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="F22" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="G22" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="B23" s="6">
-        <v>10000</v>
-      </c>
-      <c r="C23" s="6">
-        <v>10000</v>
-      </c>
-      <c r="D23" s="6">
-        <v>10000</v>
-      </c>
-      <c r="E23" s="6">
-        <v>10000</v>
-      </c>
-      <c r="F23" s="6">
-        <v>10000</v>
-      </c>
-      <c r="G23" s="6">
-        <v>10000</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" s="4"/>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B25" s="37"/>
-    </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B26" s="33">
-        <v>1</v>
-      </c>
-      <c r="C26" s="33">
-        <v>2</v>
-      </c>
-      <c r="D26" s="33">
-        <v>3</v>
-      </c>
-      <c r="E26" s="33">
-        <v>4</v>
-      </c>
-      <c r="F26" s="33">
-        <v>5</v>
-      </c>
-      <c r="G26" s="33">
-        <v>6</v>
-      </c>
-      <c r="H26" s="5" t="s">
-        <v>64</v>
-      </c>
+      <c r="B26" s="11"/>
+      <c r="C26" s="11"/>
+      <c r="D26" s="11"/>
+      <c r="E26" s="11"/>
+      <c r="F26" s="11"/>
+      <c r="G26" s="11"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B27" s="12">
+        <f>$B$4 + (B17)- B25</f>
+        <v>15000</v>
+      </c>
+      <c r="C27" s="12">
+        <f>B27 + (C17)- C25</f>
+        <v>0</v>
+      </c>
+      <c r="D27" s="12">
+        <f t="shared" ref="D27:F27" si="3">C27 + (D17)- D25</f>
+        <v>0</v>
+      </c>
+      <c r="E27" s="12">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F27" s="12">
+        <f t="shared" si="3"/>
+        <v>10000</v>
+      </c>
+      <c r="G27" s="12">
+        <f>F27 + (G17)- G25</f>
+        <v>0</v>
+      </c>
+      <c r="H27" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A28" s="38"/>
+      <c r="B28" s="39" t="s">
+        <v>17</v>
+      </c>
+      <c r="C28" s="39" t="s">
+        <v>17</v>
+      </c>
+      <c r="D28" s="39" t="s">
+        <v>17</v>
+      </c>
+      <c r="E28" s="39" t="s">
+        <v>17</v>
+      </c>
+      <c r="F28" s="39" t="s">
+        <v>17</v>
+      </c>
+      <c r="G28" s="39" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29" s="38" t="s">
+        <v>61</v>
+      </c>
+      <c r="B29" s="38">
+        <v>10000</v>
+      </c>
+      <c r="C29" s="38">
+        <v>10000</v>
+      </c>
+      <c r="D29" s="38">
+        <v>10000</v>
+      </c>
+      <c r="E29" s="38">
+        <v>10000</v>
+      </c>
+      <c r="F29" s="38">
+        <v>10000</v>
+      </c>
+      <c r="G29" s="38">
+        <v>10000</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A30" s="4"/>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B31" s="37"/>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B32" s="33">
+        <v>1</v>
+      </c>
+      <c r="C32" s="33">
+        <v>2</v>
+      </c>
+      <c r="D32" s="33">
+        <v>3</v>
+      </c>
+      <c r="E32" s="33">
+        <v>4</v>
+      </c>
+      <c r="F32" s="33">
+        <v>5</v>
+      </c>
+      <c r="G32" s="33">
+        <v>6</v>
+      </c>
+      <c r="H32" s="5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" s="46" t="s">
         <v>65</v>
       </c>
-      <c r="H27" s="38">
-        <f>SUMPRODUCT(B10:G10, B21:G21)</f>
-        <v>6312.5</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28" s="2" t="s">
+      <c r="B33" s="46"/>
+      <c r="C33" s="46"/>
+      <c r="D33" s="46"/>
+      <c r="E33" s="46"/>
+      <c r="F33" s="46"/>
+      <c r="G33" s="46"/>
+      <c r="H33" s="47">
+        <f>SUMPRODUCT(B11:G11, B27:G27)</f>
+        <v>15800</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" s="46" t="s">
+        <v>72</v>
+      </c>
+      <c r="B34" s="46"/>
+      <c r="C34" s="46"/>
+      <c r="D34" s="46"/>
+      <c r="E34" s="46"/>
+      <c r="F34" s="46"/>
+      <c r="G34" s="46"/>
+      <c r="H34" s="47">
+        <f>SUMPRODUCT(B16:G16,B12:G12)</f>
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" s="46" t="s">
         <v>66</v>
       </c>
-      <c r="H28" s="38">
-        <f>SUMPRODUCT(B9:G9,B13:G13)</f>
-        <v>1529250</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="H29" s="39">
-        <f>SUM(H27:H28)</f>
-        <v>1535562.5</v>
+      <c r="B35" s="46"/>
+      <c r="C35" s="46"/>
+      <c r="D35" s="46"/>
+      <c r="E35" s="46"/>
+      <c r="F35" s="46"/>
+      <c r="G35" s="46"/>
+      <c r="H35" s="48">
+        <f>SUMPRODUCT(B10:G10,B17:G17)</f>
+        <v>1528750</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H36" s="42">
+        <f>SUM(H33:H35)</f>
+        <v>1604550</v>
       </c>
     </row>
   </sheetData>
